--- a/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-acylcarnitine-dbs.xlsx
+++ b/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-acylcarnitine-dbs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:48:20+00:00</t>
+    <t>2026-08-28T15:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-acylcarnitine-dbs.xlsx
+++ b/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-acylcarnitine-dbs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:01:21+00:00</t>
+    <t>2026-08-28T15:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Acylcarnitin- und Carnitin-Analyte, die in Trockenblut (dried blood spot) bestimmt werden — die Messgrößen des MS/MS-Acylcarnitinprofils im Neugeborenenscreening (Fettsäureoxidationsstörungen, Organoazidopathien, Carnitinzyklusdefekte).</t>
+    <t>Acylcarnitin- und Carnitin-Analyte in Trockenblut (dried blood spot) — die Messgrößen des MS/MS-Acylcarnitinprofils im Neugeborenenscreening (Fettsäureoxidationsstörungen, Organoazidopathien, Carnitinzyklusdefekte). Abgeleitet aus der LOINC-SNOMED-Ontologie und deshalb NICHT vollständig gegenüber LOINC: enthalten ist der nach SNOMED gemappte Teil. Für die lückenlose Menge siehe mii-vs-seltene-nbs-dbs-all.</t>
   </si>
   <si>
     <t>Purpose</t>
